--- a/minecraft/excel/列车车站规划.xlsx
+++ b/minecraft/excel/列车车站规划.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duckhome\projects\MSVS\Source\Repos\yazicbs.github.io.online\minecraft\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF2A756-2B3C-4486-902A-776B985867F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A87F1B6-1150-4144-A40F-61CE278110F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
   <si>
     <t>图例：</t>
   </si>
@@ -168,6 +168,10 @@
   </si>
   <si>
     <t>繁花苑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜂谷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -289,7 +293,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -357,6 +361,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1000,8 +1007,8 @@
       <c r="AR14" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AS14" s="8" t="s">
-        <v>42</v>
+      <c r="AS14" s="23" t="s">
+        <v>49</v>
       </c>
       <c r="AT14" s="20" t="s">
         <v>9</v>
